--- a/media/exports/reports/2025-12/volunteers.xlsx
+++ b/media/exports/reports/2025-12/volunteers.xlsx
@@ -692,7 +692,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>November 626.5 h</t>
+          <t>November 780.5 h</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>November 43</t>
+          <t>November 56</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>28 volunteers</t>
+          <t>26 volunteers</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
+          <t>Mental health first aid</t>
         </is>
       </c>
       <c r="B15" s="6">
@@ -816,7 +816,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Digital literacy</t>
+          <t>Community meals</t>
         </is>
       </c>
       <c r="B16" s="6">
@@ -838,7 +838,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Community meals</t>
+          <t>Digital literacy</t>
         </is>
       </c>
       <c r="B18" s="6">
@@ -849,7 +849,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Volunteer coordinator</t>
+          <t>Youth outreach</t>
         </is>
       </c>
       <c r="B19" s="6">
@@ -860,7 +860,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mental health first aid</t>
+          <t>Volunteer coordinator</t>
         </is>
       </c>
       <c r="B20" s="6">
@@ -894,7 +894,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>46 volunteers gave 683.0 h in December, against 626.5 h in November. Youth outreach drew the most (152.5 h, 22.3%).</t>
+          <t>55 volunteers gave 830.5 h in December, against 780.5 h in November. Mental health first aid drew the most (192.0 h, 23.1%).</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Mental health first aid had the fewest volunteer hours (81.5 h). Hours are up 87.9% on December last year.</t>
+          <t>Volunteer coordinator had the fewest volunteer hours (74.5 h). Hours are up 116.6% on December last year.</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -971,7 +971,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>626.5</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="9">
@@ -1023,10 +1023,10 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>626.5</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="17">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>626.5</v>
+        <v>780.5</v>
       </c>
     </row>
     <row r="25">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>363.5</v>
+        <v>383.5</v>
       </c>
     </row>
     <row r="33">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -1244,7 +1244,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Youth outreach: volunteer hours, December 2025</t>
+          <t>Mental health first aid: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>152.5</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="B41" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="42">
@@ -1299,7 +1299,7 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>Digital literacy: volunteer hours, December 2025</t>
+          <t>Community meals: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
         </is>
       </c>
       <c r="B48" s="12" t="n">
-        <v>131.5</v>
+        <v>160.5</v>
       </c>
     </row>
     <row r="49">
@@ -1335,7 +1335,7 @@
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="50">
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="B56" s="12" t="n">
-        <v>127</v>
+        <v>157.5</v>
       </c>
     </row>
     <row r="57">
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="B57" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="58">
@@ -1409,7 +1409,7 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>Community meals: volunteer hours, December 2025</t>
+          <t>Digital literacy: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="B65" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="66">
@@ -1464,7 +1464,7 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>Volunteer coordinator: volunteer hours, December 2025</t>
+          <t>Youth outreach: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>84.5</v>
+        <v>122</v>
       </c>
     </row>
     <row r="73">
@@ -1500,7 +1500,7 @@
         </is>
       </c>
       <c r="B73" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="74">
@@ -1519,7 +1519,7 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>Mental health first aid: volunteer hours, December 2025</t>
+          <t>Volunteer coordinator: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B80" s="12" t="n">
-        <v>81.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="81">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
     </row>
     <row r="82">
@@ -1578,7 +1578,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1624,7 +1624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 6:29pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
         </is>
       </c>
     </row>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>317.5</v>
+        <v>381</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" s="12">
         <f>IF(D6=0,"",C6/D6)</f>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>392</v>
+        <v>373.5</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" s="12">
         <f>IF(D7=0,"",C7/D7)</f>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>363.5</v>
+        <v>383.5</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" s="12">
         <f>IF(D8=0,"",C8/D8)</f>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>399</v>
+        <v>387.5</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" s="12">
         <f>IF(D9=0,"",C9/D9)</f>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>422</v>
+        <v>376.5</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" s="12">
         <f>IF(D10=0,"",C10/D10)</f>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>451.5</v>
+        <v>444</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E11" s="12">
         <f>IF(D11=0,"",C11/D11)</f>
@@ -1800,7 +1800,7 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>445</v>
+        <v>422.5</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>34</v>
@@ -1822,10 +1822,10 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>513</v>
+        <v>562</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E13" s="12">
         <f>IF(D13=0,"",C13/D13)</f>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E14" s="12">
         <f>IF(D14=0,"",C14/D14)</f>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>586</v>
+        <v>609.5</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E15" s="12">
         <f>IF(D15=0,"",C15/D15)</f>
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>560.5</v>
+        <v>627</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="12">
         <f>IF(D16=0,"",C16/D16)</f>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>625.5</v>
+        <v>708.5</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E17" s="12">
         <f>IF(D17=0,"",C17/D17)</f>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>669.5</v>
+        <v>817</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E18" s="12">
         <f>IF(D18=0,"",C18/D18)</f>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>626.5</v>
+        <v>780.5</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E19" s="12">
         <f>IF(D19=0,"",C19/D19)</f>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>683</v>
+        <v>830.5</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="E20" s="12">
         <f>IF(D20=0,"",C20/D20)</f>
@@ -1992,7 +1992,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 6:29pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-12/volunteers.xlsx
+++ b/media/exports/reports/2025-12/volunteers.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Volunteer_hours_December">'Report'!$B$8</definedName>
-    <definedName name="Volunteers_who_did_a_shift_December">'Report'!$B$9</definedName>
-    <definedName name="Hours_per_volunteer_December">'Report'!$B$10</definedName>
-    <definedName name="December_last_year">'Report'!$B$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$35</definedName>
+    <definedName name="Volunteer_hours_December">'Report'!$B$9</definedName>
+    <definedName name="Volunteers_who_did_a_shift_December">'Report'!$B$10</definedName>
+    <definedName name="Hours_per_volunteer_December">'Report'!$B$11</definedName>
+    <definedName name="December_last_year">'Report'!$B$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$82</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$E$20</definedName>
@@ -56,6 +56,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -76,11 +81,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,38 +118,42 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -293,12 +297,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$15:$A$20</f>
+              <f>'Report'!$A$16:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$15:$B$20</f>
+              <f>'Report'!$B$16:$B$21</f>
             </numRef>
           </val>
         </ser>
@@ -342,7 +346,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2340000"/>
@@ -666,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -692,7 +696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -700,175 +704,181 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: 830.5 h of volunteer time in December, from 55 volunteers; most went to Mental health first aid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every volunteer shift: who (a code, not a name), which program, and how many hours.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Volunteer hours, December</t>
-        </is>
-      </c>
-      <c r="B8" s="6">
-        <f>Workings!B10</f>
-        <v/>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>November 780.5 h</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volunteers who did a shift, December</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>Workings!B18</f>
-        <v/>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>November 56</t>
+          <t>Volunteer hours, December</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>Workings!B8</f>
+        <v/>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>November 780.5 h</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hours per volunteer, December</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>Workings!B26</f>
-        <v/>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>average</t>
+          <t>Volunteers who did a shift, December</t>
+        </is>
+      </c>
+      <c r="B10" s="9">
+        <f>Workings!B17</f>
+        <v/>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>November 56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Hours per volunteer, December</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>Workings!B26</f>
+        <v/>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>average</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>December last year</t>
         </is>
       </c>
-      <c r="B11" s="6">
-        <f>Workings!B34</f>
-        <v/>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="B12" s="7">
+        <f>Workings!B32</f>
+        <v/>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>26 volunteers</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Volunteer hours by program, December 2025</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Volunteer hours by program</t>
         </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Mental health first aid</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>Workings!B41</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Community meals</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>Workings!B49</f>
+          <t>Mental health first aid</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>Workings!B40</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Housing support</t>
-        </is>
-      </c>
-      <c r="B17" s="6">
-        <f>Workings!B57</f>
+          <t>Community meals</t>
+        </is>
+      </c>
+      <c r="B17" s="7">
+        <f>Workings!B48</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Digital literacy</t>
-        </is>
-      </c>
-      <c r="B18" s="6">
-        <f>Workings!B65</f>
+          <t>Housing support</t>
+        </is>
+      </c>
+      <c r="B18" s="7">
+        <f>Workings!B56</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Youth outreach</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>Workings!B73</f>
+          <t>Digital literacy</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>Workings!B64</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Youth outreach</t>
+        </is>
+      </c>
+      <c r="B20" s="7">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Volunteer coordinator</t>
         </is>
       </c>
-      <c r="B20" s="6">
-        <f>Workings!B81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="B21" s="7">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -876,64 +886,66 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Volunteer hours by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>55 volunteers gave 830.5 h in December, against 780.5 h in November. Mental health first aid drew the most (192.0 h, 23.1%).</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Volunteer coordinator had the fewest volunteer hours (74.5 h). Hours are up 116.6% on December last year.</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37"/>
+    <row r="38"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="30" min="0" max="16383" man="1"/>
+    <brk id="13" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -971,33 +983,33 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Volunteer hours, December and November</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Hours from every volunteer shift</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
@@ -1009,10 +1021,10 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="14" t="n">
         <v>830.5</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>780.5</v>
       </c>
     </row>
@@ -1022,24 +1034,24 @@
           <t>Volunteers who did a shift</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="15" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Hours per volunteer</t>
         </is>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="17">
         <f>B8/B9</f>
         <v/>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="17">
         <f>C8/C9</f>
         <v/>
       </c>
@@ -1047,27 +1059,27 @@
     <row r="11"/>
     <row r="12"/>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Volunteer hours, December and November</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Hours from every volunteer shift</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
@@ -1079,10 +1091,10 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B16" s="14" t="n">
         <v>830.5</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="14" t="n">
         <v>780.5</v>
       </c>
     </row>
@@ -1092,24 +1104,24 @@
           <t>Volunteers who did a shift</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="15" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Hours per volunteer</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="17">
         <f>B16/B17</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="17">
         <f>C16/C17</f>
         <v/>
       </c>
@@ -1117,27 +1129,27 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Volunteer hours, December and November</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>Hours from every volunteer shift</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
@@ -1149,10 +1161,10 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
+      <c r="B24" s="14" t="n">
         <v>830.5</v>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="14" t="n">
         <v>780.5</v>
       </c>
     </row>
@@ -1162,24 +1174,24 @@
           <t>Volunteers who did a shift</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="15" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Hours per volunteer</t>
         </is>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="17">
         <f>B24/B25</f>
         <v/>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <f>C24/C25</f>
         <v/>
       </c>
@@ -1187,22 +1199,22 @@
     <row r="27"/>
     <row r="28"/>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Volunteer hours, Dec 24</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>Hours from every volunteer shift</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
@@ -1214,7 +1226,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="14" t="n">
         <v>383.5</v>
       </c>
     </row>
@@ -1224,17 +1236,17 @@
           <t>Volunteers who did a shift</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B33" s="15" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Hours per volunteer</t>
         </is>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="17">
         <f>B32/B33</f>
         <v/>
       </c>
@@ -1242,22 +1254,22 @@
     <row r="35"/>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Mental health first aid: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1269,7 +1281,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B40" s="12" t="n">
+      <c r="B40" s="14" t="n">
         <v>192</v>
       </c>
     </row>
@@ -1279,17 +1291,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="18">
         <f>B40/B41</f>
         <v/>
       </c>
@@ -1297,22 +1309,22 @@
     <row r="43"/>
     <row r="44"/>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Community meals: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1324,7 +1336,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B48" s="12" t="n">
+      <c r="B48" s="14" t="n">
         <v>160.5</v>
       </c>
     </row>
@@ -1334,17 +1346,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="18">
         <f>B48/B49</f>
         <v/>
       </c>
@@ -1352,22 +1364,22 @@
     <row r="51"/>
     <row r="52"/>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Housing support: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr"/>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1379,7 +1391,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n">
+      <c r="B56" s="14" t="n">
         <v>157.5</v>
       </c>
     </row>
@@ -1389,17 +1401,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="14" t="inlineStr">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="18">
         <f>B56/B57</f>
         <v/>
       </c>
@@ -1407,22 +1419,22 @@
     <row r="59"/>
     <row r="60"/>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Digital literacy: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="9" t="inlineStr">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1434,7 +1446,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n">
+      <c r="B64" s="14" t="n">
         <v>124</v>
       </c>
     </row>
@@ -1444,17 +1456,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n">
+      <c r="B65" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="14" t="inlineStr">
+      <c r="A66" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="18">
         <f>B64/B65</f>
         <v/>
       </c>
@@ -1462,22 +1474,22 @@
     <row r="67"/>
     <row r="68"/>
     <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>Youth outreach: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr"/>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1489,7 +1501,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n">
+      <c r="B72" s="14" t="n">
         <v>122</v>
       </c>
     </row>
@@ -1499,17 +1511,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n">
+      <c r="B73" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="14" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B74" s="16">
+      <c r="B74" s="18">
         <f>B72/B73</f>
         <v/>
       </c>
@@ -1517,22 +1529,22 @@
     <row r="75"/>
     <row r="76"/>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>Volunteer coordinator: volunteer hours, December 2025</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="A78" s="11" t="inlineStr">
         <is>
           <t>Hours from shifts on this program</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="inlineStr"/>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="A79" s="5" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1544,7 +1556,7 @@
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n">
+      <c r="B80" s="14" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -1554,17 +1566,17 @@
           <t>All volunteer hours</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n">
+      <c r="B81" s="14" t="n">
         <v>830.5</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="14" t="inlineStr">
+      <c r="A82" s="16" t="inlineStr">
         <is>
           <t>Share</t>
         </is>
       </c>
-      <c r="B82" s="16">
+      <c r="B82" s="18">
         <f>B80/B81</f>
         <v/>
       </c>
@@ -1578,7 +1590,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1624,364 +1636,364 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 11:41pm</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Volunteer hours</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Volunteers</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Hours per volunteer</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="14" t="n">
         <v>381</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="14">
         <f>IF(D6=0,"",C6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="14" t="n">
         <v>373.5</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <f>IF(D7=0,"",C7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="14" t="n">
         <v>383.5</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="15" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="14">
         <f>IF(D8=0,"",C8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="14" t="n">
         <v>387.5</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="15" t="n">
         <v>25</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <f>IF(D9=0,"",C9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="14" t="n">
         <v>376.5</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <f>IF(D10=0,"",C10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="14" t="n">
         <v>444</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <f>IF(D11=0,"",C11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="14" t="n">
         <v>422.5</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <f>IF(D12=0,"",C12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="14" t="n">
         <v>562</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="14">
         <f>IF(D13=0,"",C13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="14" t="n">
         <v>568</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="14">
         <f>IF(D14=0,"",C14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="14" t="n">
         <v>609.5</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="14">
         <f>IF(D15=0,"",C15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="14" t="n">
         <v>627</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="15" t="n">
         <v>42</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <f>IF(D16=0,"",C16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="14" t="n">
         <v>708.5</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="15" t="n">
         <v>47</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <f>IF(D17=0,"",C17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="14" t="n">
         <v>817</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="15" t="n">
         <v>54</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="14">
         <f>IF(D18=0,"",C18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="14" t="n">
         <v>780.5</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="14">
         <f>IF(D19=0,"",C19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="14" t="n">
         <v>830.5</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="14">
         <f>IF(D20=0,"",C20/D20)</f>
         <v/>
       </c>
@@ -1992,7 +2004,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 11:41pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 volunteers.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
